--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Deals of the Day" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="API Keys Blueprint" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,14 +44,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F2F4F7"/>
+        <bgColor rgb="00F2F4F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,15 +73,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,111 +444,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Property Address</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Current List Price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Neighborhood Average</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Est. Discount %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Market Status</t>
+          <t>Detected API Response Keys</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>123 Main St</t>
+          <t>ERROR: Vault credentials or data pull returned empty.</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>$350,000</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>380000</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>789 Pine Rd</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>$420,000!!</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>101 Maple Dr</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>$250,000</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>260000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -447,24 +447,33 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="57" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Detected API Response Keys</t>
+          <t>Available API Column Keys</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sample Raw Data Example</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ERROR: Vault credentials or data pull returned empty.</t>
+          <t>ERROR</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>No data returned from API.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -444,11 +444,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,12 +466,324 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>No data returned from API.</t>
+          <t>9910-Royal-Ln,-Dallas,-TX-75231</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>formattedAddress</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>9910 Royal Ln, Dallas, TX 75231</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>addressLine1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>9910 Royal Ln</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>addressLine2</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>stateFips</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>zipCode</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>75231</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>countyFips</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>32.893711</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>-96.724037</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>propertyType</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>bedrooms</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>bathrooms</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>squareFootage</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>lotSize</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>277782</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>yearBuilt</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>listingType</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>listedDate</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T00:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>removedDate</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>createdDate</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2020-02-15T00:55:57.888Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>lastSeenDate</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T03:44:44.769Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>daysOnMarket</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>{'2025-06-04': {'event': 'Rental Listing', 'price'</t>
         </is>
       </c>
     </row>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -444,11 +444,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,324 +466,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9910-Royal-Ln,-Dallas,-TX-75231</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>formattedAddress</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>9910 Royal Ln, Dallas, TX 75231</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>addressLine1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>9910 Royal Ln</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>addressLine2</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>stateFips</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>zipCode</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>75231</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>county</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>countyFips</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>32.893711</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>-96.724037</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>propertyType</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>bedrooms</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>bathrooms</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>squareFootage</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>lotSize</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>277782</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>yearBuilt</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>listingType</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>listedDate</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-16T00:00:00.000Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>removedDate</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>createdDate</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2020-02-15T00:55:57.888Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>lastSeenDate</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-16T03:44:44.769Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>daysOnMarket</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>history</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>{'2025-06-04': {'event': 'Rental Listing', 'price'</t>
+          <t>No data returned from API.</t>
         </is>
       </c>
     </row>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -444,11 +444,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,12 +466,300 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>No data returned from API.</t>
+          <t>1212-Singleton-Blvd,-Apt-3051,-Dallas,-TX-75212</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>formattedAddress</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1212 Singleton Blvd, Apt 3051, Dallas, TX 75212</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>addressLine1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1212 Singleton Blvd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>addressLine2</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Apt 3051</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>stateFips</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>zipCode</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>75212</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>countyFips</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>32.777428</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>-96.841164</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>propertyType</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>bedrooms</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>bathrooms</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>squareFootage</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>listingType</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>listedDate</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T00:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>removedDate</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>createdDate</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T00:00:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>lastSeenDate</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T03:48:07.885Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>daysOnMarket</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>{'2026-05-17': {'event': 'Rental Listing', 'price'</t>
         </is>
       </c>
     </row>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1212-Singleton-Blvd,-Apt-3051,-Dallas,-TX-75212</t>
+          <t>9101-Country-Creek-Dr,-Apt-308,-Houston,-TX-77036</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1212 Singleton Blvd, Apt 3051, Dallas, TX 75212</t>
+          <t>9101 Country Creek Dr, Apt 308, Houston, TX 77036</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1212 Singleton Blvd</t>
+          <t>9101 Country Creek Dr</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Apt 3051</t>
+          <t>Apt 308</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>75212</t>
+          <t>77036</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Harris</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>32.777428</t>
+          <t>29.680748</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>-96.841164</t>
+          <t>-95.54752</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -651,115 +651,175 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>850</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>yearBuilt</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>1980</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>listingType</t>
+          <t>price</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>900</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>listedDate</t>
+          <t>listingType</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T00:00:00.000Z</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>removedDate</t>
+          <t>listedDate</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2026-03-02T00:00:00.000Z</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>createdDate</t>
+          <t>removedDate</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T00:00:00.000Z</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>lastSeenDate</t>
+          <t>createdDate</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T03:48:07.885Z</t>
+          <t>2026-01-14T00:00:00.000Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>daysOnMarket</t>
+          <t>lastSeenDate</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2026-05-17T03:42:57.558Z</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>daysOnMarket</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>mlsName</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>mlsNumber</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>10473147</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>listingAgent</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'name': 'Allen Abouekde', 'phone': '7139951177', </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>listingOffice</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Copperwood Management Co.', 'phone': '71</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>history</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>{'2026-05-17': {'event': 'Rental Listing', 'price'</t>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>{'2026-01-13': {'event': 'Rental Listing', 'price'</t>
         </is>
       </c>
     </row>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9101-Country-Creek-Dr,-Apt-308,-Houston,-TX-77036</t>
+          <t>1212-Singleton-Blvd,-Apt-3051,-Dallas,-TX-75212</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9101 Country Creek Dr, Apt 308, Houston, TX 77036</t>
+          <t>1212 Singleton Blvd, Apt 3051, Dallas, TX 75212</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9101 Country Creek Dr</t>
+          <t>1212 Singleton Blvd</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Apt 308</t>
+          <t>Apt 3051</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Dallas</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>77036</t>
+          <t>75212</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Dallas</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>29.680748</t>
+          <t>32.777428</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>-95.54752</t>
+          <t>-96.841164</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Apartment</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -651,175 +651,115 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>504</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>yearBuilt</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>price</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>1561</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>listingType</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>listingType</t>
+          <t>listedDate</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>2026-05-17T00:00:00.000Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>listedDate</t>
+          <t>removedDate</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02T00:00:00.000Z</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>removedDate</t>
+          <t>createdDate</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2026-05-17T00:00:00.000Z</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>createdDate</t>
+          <t>lastSeenDate</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14T00:00:00.000Z</t>
+          <t>2026-05-17T03:48:07.885Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>lastSeenDate</t>
+          <t>daysOnMarket</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T03:42:57.558Z</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>daysOnMarket</t>
+          <t>history</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>mlsName</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>mlsNumber</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10473147</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>listingAgent</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{'name': 'Allen Abouekde', 'phone': '7139951177', </t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>listingOffice</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>{'name': 'Copperwood Management Co.', 'phone': '71</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>history</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>{'2026-01-13': {'event': 'Rental Listing', 'price'</t>
+          <t>{'2026-05-17': {'event': 'Rental Listing', 'price'</t>
         </is>
       </c>
     </row>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1212-Singleton-Blvd,-Apt-3051,-Dallas,-TX-75212</t>
+          <t>2650-Cedar-Springs-Rd,-Apt-6630,-Dallas,-TX-75201</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1212 Singleton Blvd, Apt 3051, Dallas, TX 75212</t>
+          <t>2650 Cedar Springs Rd, Apt 6630, Dallas, TX 75201</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1212 Singleton Blvd</t>
+          <t>2650 Cedar Springs Rd</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Apt 3051</t>
+          <t>Apt 6630</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>75212</t>
+          <t>75201</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>32.777428</t>
+          <t>32.800507</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>-96.841164</t>
+          <t>-96.804695</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>768</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>2469</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T00:00:00.000Z</t>
+          <t>2026-05-18T00:00:00.000Z</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T00:00:00.000Z</t>
+          <t>2022-07-14T03:09:37.458Z</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T03:48:07.885Z</t>
+          <t>2026-05-18T03:48:48.933Z</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>{'2026-05-17': {'event': 'Rental Listing', 'price'</t>
+          <t>{'2026-04-16': {'event': 'Rental Listing', 'price'</t>
         </is>
       </c>
     </row>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -444,11 +444,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,300 +466,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2650-Cedar-Springs-Rd,-Apt-6630,-Dallas,-TX-75201</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>formattedAddress</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2650 Cedar Springs Rd, Apt 6630, Dallas, TX 75201</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>addressLine1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2650 Cedar Springs Rd</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>addressLine2</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Apt 6630</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>stateFips</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>zipCode</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>75201</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>county</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>countyFips</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>32.800507</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>-96.804695</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>propertyType</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>bedrooms</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>bathrooms</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>squareFootage</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2469</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>listingType</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>listedDate</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T00:00:00.000Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>removedDate</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>createdDate</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-14T03:09:37.458Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>lastSeenDate</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T03:48:48.933Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>daysOnMarket</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>history</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>{'2026-04-16': {'event': 'Rental Listing', 'price'</t>
+          <t>No data returned from API.</t>
         </is>
       </c>
     </row>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -444,36 +444,561 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
+    <col width="142" customWidth="1" min="20" max="20"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="156" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Available API Column Keys</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sample Raw Data Example</t>
+          <t>formattedAddress</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>addressLine1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>addressLine2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>stateFips</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>zipCode</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>countyFips</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>propertyType</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>bedrooms</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>bathrooms</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>squareFootage</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>yearBuilt</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>lotSize</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>assessorID</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>legalDescription</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>subdivision</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>zoning</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>features</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>10700-Woodmeadow-Pkwy,-Dallas,-TX-75228</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>No data returned from API.</t>
-        </is>
-      </c>
+          <t>10700 Woodmeadow Pkwy, Dallas, TX 75228</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>10700 Woodmeadow Pkwy</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>75228</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>32.846039</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-96.638577</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>10911-Woodmeadow-Pkwy,-Dallas,-TX-75228</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>10911 Woodmeadow Pkwy, Dallas, TX 75228</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>10911 Woodmeadow Pkwy</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>75228</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>32.846812</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-96.641226</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>10500-Lake-June-Rd,-Apt-H5,-Dallas,-TX-75217</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>10500 Lake June Rd, Apt H5, Dallas, TX 75217</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10500 Lake June Rd</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Apt H5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75217</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>32.732575</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-96.644336</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1082</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>337154</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>00C08130000H00005</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>CANTERBURY CROSSING PH I-VIII BLK A/6683 LOT 2 ACS 7.74 BLDG H UNIT 5 CE 0.8% INT201500173995 DD04142014 CO-DC 6683 00A 00200 3006683 00A</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>CANTERBURY CROSSING PH 01-08</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Z164</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>{'cooling': True, 'coolingType': 'Central', 'exteriorType': 'Brick Veneer', 'floorCount': 2, 'heating': True, 'heatingType': 'Central', 'unitCount': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>801-N-Bishop-Ave,---2-201,-Dallas,-TX-75208</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>801 N Bishop Ave, # 2-201, Dallas, TX 75208</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>801 N Bishop Ave</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t># 2-201</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75208</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>32.752524</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-96.828301</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>1095</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1400-Browder-St,-Dallas,-TX-75215</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1400 Browder St, Dallas, TX 75215</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1400 Browder St</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>75215</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>32.771585</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-96.79193100000001</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -444,12 +444,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:AF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -466,10 +466,19 @@
     <col width="25" customWidth="1" min="17" max="17"/>
     <col width="25" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="142" customWidth="1" min="20" max="20"/>
-    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
     <col width="25" customWidth="1" min="22" max="22"/>
-    <col width="156" customWidth="1" min="23" max="23"/>
+    <col width="29" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="24" max="24"/>
+    <col width="29" customWidth="1" min="25" max="25"/>
+    <col width="29" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="25" customWidth="1" min="29" max="29"/>
+    <col width="151" customWidth="1" min="30" max="30"/>
+    <col width="153" customWidth="1" min="31" max="31"/>
+    <col width="750" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,57 +564,106 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>lotSize</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>yearBuilt</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>lotSize</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>assessorID</t>
+          <t>hoa</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>legalDescription</t>
+          <t>status</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>subdivision</t>
+          <t>price</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>zoning</t>
+          <t>listingType</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>listedDate</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>removedDate</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>createdDate</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>lastSeenDate</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>daysOnMarket</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mlsName</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mlsNumber</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>listingAgent</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>listingOffice</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>history</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10700-Woodmeadow-Pkwy,-Dallas,-TX-75228</t>
+          <t>18333-Roehampton-Dr,-Apt-622,-Dallas,-TX-75252</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>10700 Woodmeadow Pkwy, Dallas, TX 75228</t>
+          <t>18333 Roehampton Dr, Apt 622, Dallas, TX 75252</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>10700 Woodmeadow Pkwy</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>18333 Roehampton Dr</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apt 622</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Dallas</t>
@@ -623,63 +681,122 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>75228</t>
+          <t>75252</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>085</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>32.846039</v>
+        <v>33.001432</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-96.638577</v>
+        <v>-96.803241</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>512</v>
+        <v>737</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1983</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+        <v>915</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 256}</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>149999</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-15T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:11:14.800Z</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>21153992</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Hannah Clark', 'phone': '9035390714', 'email': 'hannahclarkrealtor@gmail.com', 'website': 'https://hannahclark.texaspremierrealty.com/'}</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Texas Premier Realty', 'phone': '8005449885', 'email': 'dzipp@satx.rr.com', 'website': 'www.darylzipp.com'}</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>{'2026-01-14': {'event': 'Sale Listing', 'price': 149999, 'listingType': 'Standard', 'listedDate': '2026-01-14T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 125}}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10911-Woodmeadow-Pkwy,-Dallas,-TX-75228</t>
+          <t>5608-Stone-Cliff-Ct,-Dallas,-TX-75287</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>10911 Woodmeadow Pkwy, Dallas, TX 75228</t>
+          <t>5608 Stone Cliff Ct, Dallas, TX 75287</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>10911 Woodmeadow Pkwy</t>
+          <t>5608 Stone Cliff Ct</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -700,70 +817,125 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>75228</t>
+          <t>75287</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>085</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>32.846812</v>
+        <v>32.989302</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-96.641226</v>
+        <v>-96.817149</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>652</v>
+        <v>8350</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1985</v>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
+        <v>13068</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 264}</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-13T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:11:14.775Z</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>21146053</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Noe De Leon', 'phone': '2142079093', 'email': 'info@identityhouserealestate.com', 'website': 'http://www.identityhouserealestate.com'}</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Exp Realty', 'phone': '8885197431', 'email': 'tx.membership@exprealty.net', 'website': 'http://www.exprealty.com'}</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>{'2024-07-12': {'event': 'Sale Listing', 'price': 2849900, 'listingType': 'Standard', 'listedDate': '2024-07-12T00:00:00.000Z', 'removedDate': '2025-02-26T00:00:00.000Z', 'daysOnMarket': 229}, '2025-04-21': {'event': 'Sale Listing', 'price': 2499999, 'listingType': 'Standard', 'listedDate': '2025-04-21T00:00:00.000Z', 'removedDate': '2025-08-05T00:00:00.000Z', 'daysOnMarket': 106}, '2025-08-08': {'event': 'Sale Listing', 'price': 2499990, 'listingType': 'Standard', 'listedDate': '2025-08-08T00:00:00.000Z', 'removedDate': '2025-11-15T00:00:00.000Z', 'daysOnMarket': 99}, '2026-01-12': {'event': 'Sale Listing', 'price': 2200000, 'listingType': 'Standard', 'listedDate': '2026-01-12T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 127}}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10500-Lake-June-Rd,-Apt-H5,-Dallas,-TX-75217</t>
+          <t>4316-N-Capistrano-Dr,-Dallas,-TX-75287</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10500 Lake June Rd, Apt H5, Dallas, TX 75217</t>
+          <t>4316 N Capistrano Dr, Dallas, TX 75287</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10500 Lake June Rd</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apt H5</t>
-        </is>
-      </c>
+          <t>4316 N Capistrano Dr</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Dallas</t>
@@ -781,90 +953,127 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75217</t>
+          <t>75287</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>085</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>32.732575</v>
+        <v>33.006685</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-96.644336</v>
+        <v>-96.836017</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>1082</v>
+        <v>2087</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1984</v>
+        <v>3920</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>337154</v>
+        <v>1988</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>00C08130000H00005</t>
+          <t>{'fee': 88}</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>CANTERBURY CROSSING PH I-VIII BLK A/6683 LOT 2 ACS 7.74 BLDG H UNIT 5 CE 0.8% INT201500173995 DD04142014 CO-DC 6683 00A 00200 3006683 00A</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>CANTERBURY CROSSING PH 01-08</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>439900</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Z164</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>{'cooling': True, 'coolingType': 'Central', 'exteriorType': 'Brick Veneer', 'floorCount': 2, 'heating': True, 'heatingType': 'Central', 'unitCount': 1}</t>
+          <t>2026-01-20T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-26T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:11:14.705Z</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>21159319</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Quinn Segars', 'phone': '4695093546', 'email': 'quinn.segars@vmrealty.homes', 'website': 'https://wmrealty.homes/'}</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'WM Realty Tx LLC', 'phone': '4694125411'}</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>{'2025-06-25': {'event': 'Sale Listing', 'price': 439900, 'listingType': 'Standard', 'listedDate': '2025-06-25T00:00:00.000Z', 'removedDate': '2025-12-09T00:00:00.000Z', 'daysOnMarket': 167}, '2026-01-20': {'event': 'Sale Listing', 'price': 439900, 'listingType': 'Standard', 'listedDate': '2026-01-20T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 119}}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>801-N-Bishop-Ave,---2-201,-Dallas,-TX-75208</t>
+          <t>18240-Midway-Rd,-Apt-1704,-Dallas,-TX-75287</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>801 N Bishop Ave, # 2-201, Dallas, TX 75208</t>
+          <t>18240 Midway Rd, Apt 1704, Dallas, TX 75287</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>801 N Bishop Ave</t>
+          <t>18240 Midway Rd</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t># 2-201</t>
+          <t>Apt 1704</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -884,61 +1093,122 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75208</t>
+          <t>75287</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>085</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>32.752524</v>
+        <v>32.999556</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-96.828301</v>
+        <v>-96.842499</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>1095</v>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
+        <v>1032</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>2178</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 510}</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-24T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-25T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:10:58.181Z</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>21162886</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Kendra Norwood', 'phone': '2143946076', 'email': 'kendranorwood@remax.net', 'website': 'http://www.relocatingspecialists.com'}</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Re/Max Innovations', 'phone': '8043869278', 'email': 'kendranorwood@remax.net'}</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>{'2026-01-24': {'event': 'Sale Listing', 'price': 230000, 'listingType': 'Standard', 'listedDate': '2026-01-24T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 115}}</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1400-Browder-St,-Dallas,-TX-75215</t>
+          <t>5819-Coolwater-Cv,-Dallas,-TX-75252</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1400 Browder St, Dallas, TX 75215</t>
+          <t>5819 Coolwater Cv, Dallas, TX 75252</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1400 Browder St</t>
+          <t>5819 Coolwater Cv</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -959,46 +1229,783 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75215</t>
+          <t>75252</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>085</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>32.988011</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-96.80840499999999</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Single Family</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>4370</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>7405</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 58}</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>1099000</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-15T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:10:58.130Z</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>21163928</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Kyle Rovinsky', 'phone': '9729898568', 'email': 'kyle.rovinsky@cbdfw.com', 'website': 'http://www.rovinskyhomes.com/'}</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Dave Perry-Miller - Preston Center', 'phone': '2142945788', 'email': 'homeinfo@daveperrymiller.com'}</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>{'2025-03-14': {'event': 'Sale Listing', 'price': 1145000, 'listingType': 'Standard', 'listedDate': '2025-03-14T00:00:00.000Z', 'removedDate': '2025-11-12T00:00:00.000Z', 'daysOnMarket': 243}, '2026-01-30': {'event': 'Sale Listing', 'price': 1099000, 'listingType': 'Standard', 'listedDate': '2026-01-30T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 109}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>5308-Ventana-Trl,-Dallas,-TX-75252</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>5308 Ventana Trl, Dallas, TX 75252</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5308 Ventana Trl</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>32.771585</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>-96.79193100000001</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Townhouse</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75252</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>085</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>33.011127</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-96.801073</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Single Family</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>3920</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>475000</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-05T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>2020-09-21T23:09:37.405Z</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:10:58.084Z</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>21171302</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Shari Samani, Broker', 'phone': '9729758381', 'email': 'sharisamani@gmail.com'}</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'WILLIAM DAVIS REALTY', 'phone': '9727326002', 'email': 'billjordan@mywdr.com'}</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>{'2025-09-10': {'event': 'Sale Listing', 'price': 497000, 'listingType': 'Standard', 'listedDate': '2025-09-10T00:00:00.000Z', 'removedDate': '2025-10-07T00:00:00.000Z', 'daysOnMarket': 27}, '2026-02-05': {'event': 'Sale Listing', 'price': 475000, 'listingType': 'Standard', 'listedDate': '2026-02-05T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 103}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>17719-Sunmeadow-Dr,-Dallas,-TX-75252</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>17719 Sunmeadow Dr, Dallas, TX 75252</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>17719 Sunmeadow Dr</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75252</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>085</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>32.994266</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-96.801677</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Single Family</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>5532</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 251}</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>365000</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-05T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:10:49.494Z</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>21153387</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Kurt Cisco', 'phone': '2147323781', 'email': 'kurtcisco@aol.com'}</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Texas Signature Realty, LLC.', 'phone': '8328762093', 'email': 'texassignaturerealty@gmail.com'}</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>{'2026-02-05': {'event': 'Sale Listing', 'price': 365000, 'listingType': 'Standard', 'listedDate': '2026-02-05T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 103}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>6144-Jereme-Trl,-Dallas,-TX-75252</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>6144 Jereme Trl, Dallas, TX 75252</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6144 Jereme Trl</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>75252</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>085</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>33.003061</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-96.79990599999999</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Single Family</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="n">
+        <v>1610</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>3920</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 108}</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>370000</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-08T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:10:49.450Z</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>21172871</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Michelle Johnson', 'phone': '8174564227', 'email': 'michelle@modernedge.realestate', 'website': 'http://www.modernedge.realestate/'}</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Modern Edge Real Estate', 'phone': '8179899192', 'email': 'michelle@modernedge.realestate', 'website': 'http://www.modernedge.realestate'}</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>{'2026-02-08': {'event': 'Sale Listing', 'price': 370000, 'listingType': 'Standard', 'listedDate': '2026-02-08T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 100}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>7319-Briarnoll-Dr,-Dallas,-TX-75252</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>7319 Briarnoll Dr, Dallas, TX 75252</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7319 Briarnoll Dr</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>75252</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>085</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>32.995163</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-96.778902</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Single Family</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>2587</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>10890</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>1986</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>699000</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-10T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>2023-01-27T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:10:49.431Z</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>21176183</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Natalie Amiel', 'phone': '8184451303', 'email': 'natalieamielrealtor@gmail.com'}</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'JPAR Real Estate North Metro ', 'phone': '8006835651', 'email': 'support@jpar.com', 'website': 'https://www.jpar.com/'}</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>{'2026-02-10': {'event': 'Sale Listing', 'price': 699000, 'listingType': 'Standard', 'listedDate': '2026-02-10T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 98}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>18333-Roehampton-Dr,-Apt-313,-Dallas,-TX-75252</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>18333 Roehampton Dr, Apt 313, Dallas, TX 75252</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>18333 Roehampton Dr</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Apt 313</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75252</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>085</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>33.001432</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>-96.803241</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>737</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>1133</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 332}</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>164999</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-15T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-06T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T12:10:45.588Z</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>NTREIS</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>21180721</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Minh Hoang', 'phone': '4692538888', 'email': 'leasemeng@gmail.com', 'website': 'http://batdongsandfw.com/'}</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>{'name': 'Avignon Realty', 'phone': '9727920004', 'email': 'van@avignonrealty.com', 'website': 'www.avignonrealty.com'}</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>{'2024-10-05': {'event': 'Sale Listing', 'price': 170000, 'listingType': 'Standard', 'listedDate': '2024-10-05T00:00:00.000Z', 'removedDate': '2024-11-02T00:00:00.000Z', 'daysOnMarket': 28}, '2026-02-15': {'event': 'Sale Listing', 'price': 164999, 'listingType': 'Standard', 'listedDate': '2026-02-15T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 93}}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -449,7 +449,7 @@
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
     <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -468,17 +468,17 @@
     <col width="25" customWidth="1" min="19" max="19"/>
     <col width="25" customWidth="1" min="20" max="20"/>
     <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="25" customWidth="1" min="22" max="22"/>
-    <col width="29" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
+    <col width="29" customWidth="1" min="22" max="22"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
+    <col width="29" customWidth="1" min="24" max="24"/>
     <col width="29" customWidth="1" min="25" max="25"/>
-    <col width="29" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
     <col width="25" customWidth="1" min="27" max="27"/>
     <col width="25" customWidth="1" min="28" max="28"/>
-    <col width="25" customWidth="1" min="29" max="29"/>
-    <col width="151" customWidth="1" min="30" max="30"/>
-    <col width="153" customWidth="1" min="31" max="31"/>
-    <col width="750" customWidth="1" min="32" max="32"/>
+    <col width="145" customWidth="1" min="29" max="29"/>
+    <col width="144" customWidth="1" min="30" max="30"/>
+    <col width="935" customWidth="1" min="31" max="31"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,99 +574,95 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>listingType</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>listedDate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>removedDate</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>createdDate</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>lastSeenDate</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>daysOnMarket</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mlsName</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mlsNumber</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>listingAgent</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>listingOffice</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>hoa</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>listingType</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>listedDate</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>removedDate</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>createdDate</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>lastSeenDate</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>daysOnMarket</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>mlsName</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>mlsNumber</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>listingAgent</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>listingOffice</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>history</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>18333-Roehampton-Dr,-Apt-622,-Dallas,-TX-75252</t>
+          <t>2514-Haverhill-Dr,-Houston,-TX-77008</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18333 Roehampton Dr, Apt 622, Dallas, TX 75252</t>
+          <t>2514 Haverhill Dr, Houston, TX 77008</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>18333 Roehampton Dr</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apt 622</t>
-        </is>
-      </c>
+          <t>2514 Haverhill Dr</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -681,128 +677,124 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>75252</t>
+          <t>77008</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>33.001432</v>
+        <v>29.799585</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-96.803241</v>
+        <v>-95.444349</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>737</v>
+        <v>2190</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>915</v>
+        <v>7588</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1985</v>
+        <v>1965</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 256}</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>149999</v>
+      <c r="T2" s="2" t="n">
+        <v>689900</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-14T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-21T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:11:14.800Z</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="n">
-        <v>125</v>
+          <t>2026-05-18T12:10:29.493Z</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>74706633</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>21153992</t>
+          <t>{'name': 'Joshua Marks', 'phone': '8328707009', 'email': 'joshua.marks@exprealty.com'}</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Hannah Clark', 'phone': '9035390714', 'email': 'hannahclarkrealtor@gmail.com', 'website': 'https://hannahclark.texaspremierrealty.com/'}</t>
+          <t>{'name': 'Spyglass Realty', 'phone': '5127590889', 'email': 'aprilcostenbader@spyglassrealty.com', 'website': 'www.spyglassrealty.com'}</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Texas Premier Realty', 'phone': '8005449885', 'email': 'dzipp@satx.rr.com', 'website': 'www.darylzipp.com'}</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>{'2026-01-14': {'event': 'Sale Listing', 'price': 149999, 'listingType': 'Standard', 'listedDate': '2026-01-14T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 125}}</t>
-        </is>
-      </c>
+          <t>{'2024-08-23': {'event': 'Sale Listing', 'price': 769900, 'listingType': 'Standard', 'listedDate': '2024-08-23T00:00:00.000Z', 'removedDate': '2024-11-22T00:00:00.000Z', 'daysOnMarket': 91}, '2024-11-22': {'event': 'Sale Listing', 'price': 739000, 'listingType': 'Standard', 'listedDate': '2024-11-22T00:00:00.000Z', 'removedDate': '2025-05-01T00:00:00.000Z', 'daysOnMarket': 160}, '2025-05-17': {'event': 'Sale Listing', 'price': 712000, 'listingType': 'Standard', 'listedDate': '2025-05-17T00:00:00.000Z', 'removedDate': '2025-10-20T00:00:00.000Z', 'daysOnMarket': 156}, '2026-02-26': {'event': 'Sale Listing', 'price': 699900, 'listingType': 'Standard', 'listedDate': '2026-02-26T00:00:00.000Z', 'removedDate': '2026-04-23T00:00:00.000Z', 'daysOnMarket': 56}, '2026-04-23': {'event': 'Sale Listing', 'price': 689900, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>5608-Stone-Cliff-Ct,-Dallas,-TX-75287</t>
+          <t>Grace-Ln,-Houston,-TX-77021</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5608 Stone Cliff Ct, Dallas, TX 75287</t>
+          <t>Grace Ln, Houston, TX 77021</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>5608 Stone Cliff Ct</t>
+          <t>Grace Ln</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -817,128 +809,116 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>32.989302</v>
+        <v>29.699585</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-96.817149</v>
+        <v>-95.342327</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Single Family</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>8350</v>
-      </c>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="n">
-        <v>13068</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>1995</v>
-      </c>
+        <v>4561</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 264}</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>2200000</v>
+      <c r="T3" s="2" t="n">
+        <v>125000</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-12T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2024-07-13T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:11:14.775Z</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>127</v>
+          <t>2026-05-18T12:10:29.492Z</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>3463363</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21146053</t>
+          <t>{'name': 'Jennifer Allen', 'phone': '2817331351', 'email': 'jenn@jenniferallenteam.com', 'website': 'http://www.jenniferallenteam.com'}</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Noe De Leon', 'phone': '2142079093', 'email': 'info@identityhouserealestate.com', 'website': 'http://www.identityhouserealestate.com'}</t>
+          <t>{'name': 'Exp Realty LLC', 'phone': '8885197431', 'email': 'djones@wandjlaw.com'}</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Exp Realty', 'phone': '8885197431', 'email': 'tx.membership@exprealty.net', 'website': 'http://www.exprealty.com'}</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>{'2024-07-12': {'event': 'Sale Listing', 'price': 2849900, 'listingType': 'Standard', 'listedDate': '2024-07-12T00:00:00.000Z', 'removedDate': '2025-02-26T00:00:00.000Z', 'daysOnMarket': 229}, '2025-04-21': {'event': 'Sale Listing', 'price': 2499999, 'listingType': 'Standard', 'listedDate': '2025-04-21T00:00:00.000Z', 'removedDate': '2025-08-05T00:00:00.000Z', 'daysOnMarket': 106}, '2025-08-08': {'event': 'Sale Listing', 'price': 2499990, 'listingType': 'Standard', 'listedDate': '2025-08-08T00:00:00.000Z', 'removedDate': '2025-11-15T00:00:00.000Z', 'daysOnMarket': 99}, '2026-01-12': {'event': 'Sale Listing', 'price': 2200000, 'listingType': 'Standard', 'listedDate': '2026-01-12T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 127}}</t>
-        </is>
-      </c>
+          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 125000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>4316-N-Capistrano-Dr,-Dallas,-TX-75287</t>
+          <t>11603-Vailrun-Dr,-Houston,-TX-77070</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>4316 N Capistrano Dr, Dallas, TX 75287</t>
+          <t>11603 Vailrun Dr, Houston, TX 77070</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4316 N Capistrano Dr</t>
+          <t>11603 Vailrun Dr</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -953,24 +933,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>77070</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>33.006685</v>
+        <v>29.975319</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-96.836017</v>
+        <v>-95.597576</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -984,101 +964,101 @@
         <v>2.5</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>2087</v>
+        <v>2556</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>3920</v>
+        <v>8969</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 88}</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>439900</v>
+      <c r="T4" s="2" t="n">
+        <v>347500</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-20T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>2025-06-26T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:11:14.705Z</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>119</v>
+          <t>2026-05-18T12:10:29.491Z</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>67844418</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>21159319</t>
+          <t>{'name': 'Elizabeth Wallace', 'phone': '8325197982', 'email': 'lizwallacesold@gmail.com', 'website': 'http://lizwallacesold.com/'}</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Quinn Segars', 'phone': '4695093546', 'email': 'quinn.segars@vmrealty.homes', 'website': 'https://wmrealty.homes/'}</t>
+          <t>{'name': 'RE MAX Associates Northeast', 'phone': '2813588888', 'email': 'maria.west1@remax.net', 'website': 'www.northhoustonhomes.com'}</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'WM Realty Tx LLC', 'phone': '4694125411'}</t>
+          <t>{'2026-03-31': {'event': 'Sale Listing', 'price': 359000, 'listingType': 'Standard', 'listedDate': '2026-03-31T00:00:00.000Z', 'removedDate': '2026-04-16T00:00:00.000Z', 'daysOnMarket': 16}, '2026-04-23': {'event': 'Sale Listing', 'price': 347500, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>{'2025-06-25': {'event': 'Sale Listing', 'price': 439900, 'listingType': 'Standard', 'listedDate': '2025-06-25T00:00:00.000Z', 'removedDate': '2025-12-09T00:00:00.000Z', 'daysOnMarket': 167}, '2026-01-20': {'event': 'Sale Listing', 'price': 439900, 'listingType': 'Standard', 'listedDate': '2026-01-20T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 119}}</t>
+          <t>{'fee': 63}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18240-Midway-Rd,-Apt-1704,-Dallas,-TX-75287</t>
+          <t>8206-Colonial--B-Ln,-Unit-A,-Houston,-TX-77051</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>18240 Midway Rd, Apt 1704, Dallas, TX 75287</t>
+          <t>8206 Colonial /B Ln, Unit A, Houston, TX 77051</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18240 Midway Rd</t>
+          <t>8206 Colonial /B Ln</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Apt 1704</t>
+          <t>Unit A</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1093,128 +1073,128 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>77051</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>32.999556</v>
+        <v>29.672921</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-96.842499</v>
+        <v>-95.368985</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Multi-Family</t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P5" s="2" t="n">
-        <v>1032</v>
+        <v>3396</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>2178</v>
+        <v>5000</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1982</v>
+        <v>2026</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 510}</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>230000</v>
+      <c r="T5" s="2" t="n">
+        <v>599000</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>New Construction</t>
+        </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-24T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>2026-01-25T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:10:58.181Z</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="n">
-        <v>115</v>
+          <t>2026-05-18T12:10:29.490Z</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>6194906</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>21162886</t>
+          <t>{'name': 'Jamila Hodge', 'phone': '2812425829', 'email': 'jhodgerealestate@gmail.com', 'website': 'http://cbunited.com/jamila.hodge'}</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Kendra Norwood', 'phone': '2143946076', 'email': 'kendranorwood@remax.net', 'website': 'http://www.relocatingspecialists.com'}</t>
+          <t>{'name': 'Nextgen Real Estate Properties', 'phone': '2817637232', 'email': 'jennifer@houstonhomeblueprint.com'}</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Re/Max Innovations', 'phone': '8043869278', 'email': 'kendranorwood@remax.net'}</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>{'2026-01-24': {'event': 'Sale Listing', 'price': 230000, 'listingType': 'Standard', 'listedDate': '2026-01-24T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 115}}</t>
-        </is>
-      </c>
+          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 599000, 'listingType': 'New Construction', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>5819-Coolwater-Cv,-Dallas,-TX-75252</t>
+          <t>8601-Amadwe--B-St,-Unit-A,-Houston,-TX-77051</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5819 Coolwater Cv, Dallas, TX 75252</t>
+          <t>8601 Amadwe /B St, Unit A, Houston, TX 77051</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5819 Coolwater Cv</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>8601 Amadwe /B St</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Unit A</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1229,128 +1209,124 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75252</t>
+          <t>77051</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>32.988011</v>
+        <v>29.668211</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-96.80840499999999</v>
+        <v>-95.35651300000001</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Multi-Family</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>4370</v>
+        <v>3590</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>7405</v>
+        <v>4400</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>1994</v>
+        <v>2026</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 58}</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>1099000</v>
+      <c r="T6" s="2" t="n">
+        <v>545000</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>New Construction</t>
+        </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-30T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>2025-03-15T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:10:58.130Z</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="n">
-        <v>109</v>
+          <t>2026-05-18T12:10:29.487Z</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>25293742</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>21163928</t>
+          <t>{'name': 'Moji Oladunjoye', 'phone': '8327798098'}</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Kyle Rovinsky', 'phone': '9729898568', 'email': 'kyle.rovinsky@cbdfw.com', 'website': 'http://www.rovinskyhomes.com/'}</t>
+          <t>{'name': 'Mo Maison Realty', 'phone': '8327798098', 'email': 'moji@mo-maison.com'}</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Dave Perry-Miller - Preston Center', 'phone': '2142945788', 'email': 'homeinfo@daveperrymiller.com'}</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>{'2025-03-14': {'event': 'Sale Listing', 'price': 1145000, 'listingType': 'Standard', 'listedDate': '2025-03-14T00:00:00.000Z', 'removedDate': '2025-11-12T00:00:00.000Z', 'daysOnMarket': 243}, '2026-01-30': {'event': 'Sale Listing', 'price': 1099000, 'listingType': 'Standard', 'listedDate': '2026-01-30T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 109}}</t>
-        </is>
-      </c>
+          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 545000, 'listingType': 'New Construction', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>5308-Ventana-Trl,-Dallas,-TX-75252</t>
+          <t>501-Detering-St,-Houston,-TX-77007</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5308 Ventana Trl, Dallas, TX 75252</t>
+          <t>501 Detering St, Houston, TX 77007</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5308 Ventana Trl</t>
+          <t>501 Detering St</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1365,124 +1341,124 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75252</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>33.011127</v>
+        <v>29.76682</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-96.801073</v>
+        <v>-95.416451</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>2459</v>
+        <v>2372</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>3920</v>
+        <v>2136</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>1992</v>
-      </c>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
+        <v>1999</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>475000</v>
+      <c r="T7" s="2" t="n">
+        <v>484000</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-05T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>2020-09-21T23:09:37.405Z</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:10:58.084Z</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="n">
-        <v>103</v>
+          <t>2026-05-18T12:10:29.367Z</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>48776375</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21171302</t>
+          <t>{'name': 'Leah Oliver', 'phone': '8324442669', 'email': 'leah.oliver@sothebyshomes.com', 'website': 'https://www.sothebyshomes.com/houston'}</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Shari Samani, Broker', 'phone': '9729758381', 'email': 'sharisamani@gmail.com'}</t>
+          <t>{'name': 'Compass RE Texas LLC - Westheimer', 'phone': '8328994788', 'email': 'txbroker@compass.com', 'website': 'http://www.compass.com'}</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'WILLIAM DAVIS REALTY', 'phone': '9727326002', 'email': 'billjordan@mywdr.com'}</t>
-        </is>
-      </c>
-      <c r="AF7" s="2" t="inlineStr">
-        <is>
-          <t>{'2025-09-10': {'event': 'Sale Listing', 'price': 497000, 'listingType': 'Standard', 'listedDate': '2025-09-10T00:00:00.000Z', 'removedDate': '2025-10-07T00:00:00.000Z', 'daysOnMarket': 27}, '2026-02-05': {'event': 'Sale Listing', 'price': 475000, 'listingType': 'Standard', 'listedDate': '2026-02-05T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 103}}</t>
-        </is>
-      </c>
+          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 484000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>17719-Sunmeadow-Dr,-Dallas,-TX-75252</t>
+          <t>2236-Ann-St,-Houston,-TX-77003</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17719 Sunmeadow Dr, Dallas, TX 75252</t>
+          <t>2236 Ann St, Houston, TX 77003</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17719 Sunmeadow Dr</t>
+          <t>2236 Ann St</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1497,128 +1473,124 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75252</t>
+          <t>77003</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>32.994266</v>
+        <v>29.760342</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-96.801677</v>
+        <v>-95.34624599999999</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1985</v>
+        <v>1656</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>5532</v>
+        <v>1400</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>1990</v>
+        <v>2003</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 251}</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>365000</v>
+      <c r="T8" s="2" t="n">
+        <v>310000</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-05T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-21T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:10:49.494Z</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="n">
-        <v>103</v>
+          <t>2026-05-18T12:10:29.363Z</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>8232513</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21153387</t>
+          <t>{'name': 'Marcus Ruiz', 'phone': '3462341001', 'email': 'marcruiz04@gmail.com'}</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Kurt Cisco', 'phone': '2147323781', 'email': 'kurtcisco@aol.com'}</t>
+          <t>{'name': 'Re/Max Signature', 'phone': '7139005003', 'email': 'roxie@remaxsignaturetx.com'}</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Texas Signature Realty, LLC.', 'phone': '8328762093', 'email': 'texassignaturerealty@gmail.com'}</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="inlineStr">
-        <is>
-          <t>{'2026-02-05': {'event': 'Sale Listing', 'price': 365000, 'listingType': 'Standard', 'listedDate': '2026-02-05T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 103}}</t>
-        </is>
-      </c>
+          <t>{'2025-05-20': {'event': 'Sale Listing', 'price': 310000, 'listingType': 'Standard', 'listedDate': '2025-05-20T00:00:00.000Z', 'removedDate': '2025-05-22T00:00:00.000Z', 'daysOnMarket': 2}, '2026-04-23': {'event': 'Sale Listing', 'price': 310000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>6144-Jereme-Trl,-Dallas,-TX-75252</t>
+          <t>1427-Basswood-Springs-Ct,-Houston,-TX-77062</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6144 Jereme Trl, Dallas, TX 75252</t>
+          <t>1427 Basswood Springs Ct, Houston, TX 77062</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6144 Jereme Trl</t>
+          <t>1427 Basswood Springs Ct</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1633,24 +1605,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75252</t>
+          <t>77062</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>33.003061</v>
+        <v>29.585769</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-96.79990599999999</v>
+        <v>-95.151549</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1658,103 +1630,103 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1610</v>
+        <v>2227</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>3920</v>
+        <v>11147</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 108}</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>370000</v>
+      <c r="T9" s="2" t="n">
+        <v>410000</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-08T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:10:49.450Z</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="n">
-        <v>100</v>
+          <t>2026-05-18T12:10:29.362Z</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>70583215</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21172871</t>
+          <t>{'name': 'Michael Nassif', 'email': 'michael.nassif@nrerealty.com', 'website': 'http://nrerealty.com'}</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Michelle Johnson', 'phone': '8174564227', 'email': 'michelle@modernedge.realestate', 'website': 'http://www.modernedge.realestate/'}</t>
+          <t>{'name': 'Nre Realty', 'phone': '2813007189', 'email': 'michael.nassif@nrerealty.com', 'website': 'http://nrerealty.com'}</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Modern Edge Real Estate', 'phone': '8179899192', 'email': 'michelle@modernedge.realestate', 'website': 'http://www.modernedge.realestate'}</t>
+          <t>{'2026-02-27': {'event': 'Sale Listing', 'price': 430000, 'listingType': 'Standard', 'listedDate': '2026-02-27T00:00:00.000Z', 'removedDate': '2026-03-26T00:00:00.000Z', 'daysOnMarket': 27}, '2026-04-23': {'event': 'Sale Listing', 'price': 410000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
         </is>
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>{'2026-02-08': {'event': 'Sale Listing', 'price': 370000, 'listingType': 'Standard', 'listedDate': '2026-02-08T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 100}}</t>
+          <t>{'fee': 71}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>7319-Briarnoll-Dr,-Dallas,-TX-75252</t>
+          <t>8903-Railton-St,-Houston,-TX-77080</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7319 Briarnoll Dr, Dallas, TX 75252</t>
+          <t>8903 Railton St, Houston, TX 77080</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7319 Briarnoll Dr</t>
+          <t>8903 Railton St</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1769,24 +1741,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75252</t>
+          <t>77080</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>32.995163</v>
+        <v>29.828289</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-96.778902</v>
+        <v>-95.511835</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1797,100 +1769,96 @@
         <v>4</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2587</v>
+        <v>2174</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>10890</v>
+        <v>9361</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>1986</v>
-      </c>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
+        <v>1960</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>699000</v>
+      <c r="T10" s="2" t="n">
+        <v>425000</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-10T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-29T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>2023-01-27T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:10:49.431Z</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>98</v>
+          <t>2026-05-18T12:10:29.361Z</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>46758823</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21176183</t>
+          <t>{'name': 'Jordana Ford', 'phone': '2817886241', 'email': 'info@jordanaford.com', 'website': 'http://www.homeinwesthouston.com'}</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Natalie Amiel', 'phone': '8184451303', 'email': 'natalieamielrealtor@gmail.com'}</t>
+          <t>{'name': 'Compass RE Texas LLC - The Heights', 'phone': '2817299246', 'email': 'txbroker@compass.com', 'website': 'http://www.compass.com'}</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'JPAR Real Estate North Metro ', 'phone': '8006835651', 'email': 'support@jpar.com', 'website': 'https://www.jpar.com/'}</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="inlineStr">
-        <is>
-          <t>{'2026-02-10': {'event': 'Sale Listing', 'price': 699000, 'listingType': 'Standard', 'listedDate': '2026-02-10T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 98}}</t>
-        </is>
-      </c>
+          <t>{'2025-10-23': {'event': 'Sale Listing', 'price': 460000, 'listingType': 'Standard', 'listedDate': '2025-10-23T00:00:00.000Z', 'removedDate': '2026-01-07T00:00:00.000Z', 'daysOnMarket': 76}, '2026-01-07': {'event': 'Sale Listing', 'price': 438000, 'listingType': 'Standard', 'listedDate': '2026-01-07T00:00:00.000Z', 'removedDate': '2026-04-23T00:00:00.000Z', 'daysOnMarket': 106}, '2026-04-23': {'event': 'Sale Listing', 'price': 425000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>18333-Roehampton-Dr,-Apt-313,-Dallas,-TX-75252</t>
+          <t>18010-Quiet-Stream-Ct,-Houston,-TX-77095</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>18333 Roehampton Dr, Apt 313, Dallas, TX 75252</t>
+          <t>18010 Quiet Stream Ct, Houston, TX 77095</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18333 Roehampton Dr</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Apt 313</t>
-        </is>
-      </c>
+          <t>18010 Quiet Stream Ct</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1905,105 +1873,105 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75252</t>
+          <t>77095</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>085</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>33.001432</v>
+        <v>29.889556</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-96.803241</v>
+        <v>-95.682858</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>737</v>
+        <v>2461</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>1133</v>
+        <v>8075</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>1985</v>
+        <v>1994</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 332}</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>164999</v>
+      <c r="T11" s="2" t="n">
+        <v>349000</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-15T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr"/>
+          <t>2026-04-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24T00:00:00.000Z</t>
+        </is>
+      </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>2024-10-06T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18T12:10:45.588Z</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="n">
-        <v>93</v>
+          <t>2026-05-18T12:10:29.360Z</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>NTREIS</t>
+          <t>56512593</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21180721</t>
+          <t>{'name': 'Tina Vu', 'phone': '8327329772'}</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Hoang', 'phone': '4692538888', 'email': 'leasemeng@gmail.com', 'website': 'http://batdongsandfw.com/'}</t>
+          <t>{'name': 'Walzel Properties', 'phone': '7135044874', 'email': 'shellywazel@gmail.com', 'website': 'http://www.walzelproperties.com'}</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Avignon Realty', 'phone': '9727920004', 'email': 'van@avignonrealty.com', 'website': 'www.avignonrealty.com'}</t>
+          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 349000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>{'2024-10-05': {'event': 'Sale Listing', 'price': 170000, 'listingType': 'Standard', 'listedDate': '2024-10-05T00:00:00.000Z', 'removedDate': '2024-11-02T00:00:00.000Z', 'daysOnMarket': 28}, '2026-02-15': {'event': 'Sale Listing', 'price': 164999, 'listingType': 'Standard', 'listedDate': '2026-02-15T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 93}}</t>
+          <t>{'fee': 73}</t>
         </is>
       </c>
     </row>

--- a/Premium_Undervalued_Deals.xlsx
+++ b/Premium_Undervalued_Deals.xlsx
@@ -447,9 +447,9 @@
   <dimension ref="A1:AF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -475,9 +475,9 @@
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="25" customWidth="1" min="27" max="27"/>
     <col width="25" customWidth="1" min="28" max="28"/>
-    <col width="145" customWidth="1" min="29" max="29"/>
-    <col width="144" customWidth="1" min="30" max="30"/>
-    <col width="935" customWidth="1" min="31" max="31"/>
+    <col width="173" customWidth="1" min="29" max="29"/>
+    <col width="159" customWidth="1" min="30" max="30"/>
+    <col width="176" customWidth="1" min="31" max="31"/>
     <col width="25" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
@@ -646,23 +646,23 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2514-Haverhill-Dr,-Houston,-TX-77008</t>
+          <t>604-Fletcher-St,-Austin,-TX-78704</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2514 Haverhill Dr, Houston, TX 77008</t>
+          <t>604 Fletcher St, Austin, TX 78704</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2514 Haverhill Dr</t>
+          <t>604 Fletcher St</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -677,44 +677,44 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>77008</t>
+          <t>78704</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>29.799585</v>
+        <v>30.243643</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-95.444349</v>
+        <v>-97.758833</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Multi-Family</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>2190</v>
+        <v>2400</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>7588</v>
+        <v>7928</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1965</v>
+        <v>2001</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="T2" s="2" t="n">
-        <v>689900</v>
+        <v>1999050</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
@@ -731,46 +731,46 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2021-09-27T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2024-06-21T00:00:00.000Z</t>
+          <t>2021-09-28T15:37:36.358Z</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.493Z</t>
+          <t>2026-05-18T12:07:46.161Z</t>
         </is>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>26</v>
+        <v>1695</v>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74706633</t>
+          <t>6461334</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Joshua Marks', 'phone': '8328707009', 'email': 'joshua.marks@exprealty.com'}</t>
+          <t>{'name': 'George Liebes', 'phone': '5124584449', 'email': 'caldco@msn.com'}</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Spyglass Realty', 'phone': '5127590889', 'email': 'aprilcostenbader@spyglassrealty.com', 'website': 'www.spyglassrealty.com'}</t>
+          <t>{'name': 'The Caldwell Company', 'phone': '5124584449', 'email': 'caldco@msn.com'}</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>{'2024-08-23': {'event': 'Sale Listing', 'price': 769900, 'listingType': 'Standard', 'listedDate': '2024-08-23T00:00:00.000Z', 'removedDate': '2024-11-22T00:00:00.000Z', 'daysOnMarket': 91}, '2024-11-22': {'event': 'Sale Listing', 'price': 739000, 'listingType': 'Standard', 'listedDate': '2024-11-22T00:00:00.000Z', 'removedDate': '2025-05-01T00:00:00.000Z', 'daysOnMarket': 160}, '2025-05-17': {'event': 'Sale Listing', 'price': 712000, 'listingType': 'Standard', 'listedDate': '2025-05-17T00:00:00.000Z', 'removedDate': '2025-10-20T00:00:00.000Z', 'daysOnMarket': 156}, '2026-02-26': {'event': 'Sale Listing', 'price': 699900, 'listingType': 'Standard', 'listedDate': '2026-02-26T00:00:00.000Z', 'removedDate': '2026-04-23T00:00:00.000Z', 'daysOnMarket': 56}, '2026-04-23': {'event': 'Sale Listing', 'price': 689900, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+          <t>{'2021-09-27': {'event': 'Sale Listing', 'price': 1999050, 'listingType': 'Standard', 'listedDate': '2021-09-27T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 1695}}</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr"/>
@@ -778,23 +778,23 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Grace-Ln,-Houston,-TX-77021</t>
+          <t>10731-Menchaca-Rd,-Austin,-TX-78748</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Grace Ln, Houston, TX 77021</t>
+          <t>10731 Menchaca Rd, Austin, TX 78748</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Grace Ln</t>
+          <t>10731 Menchaca Rd</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -809,24 +809,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>77021</t>
+          <t>78748</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>29.699585</v>
+        <v>30.162371</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-95.342327</v>
+        <v>-97.83089</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="n">
-        <v>4561</v>
+        <v>205603</v>
       </c>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="T3" s="2" t="n">
-        <v>125000</v>
+        <v>2250000</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
@@ -855,46 +855,46 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2022-12-01T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24T00:00:00.000Z</t>
+          <t>2022-12-02T08:47:00.585Z</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.492Z</t>
+          <t>2026-05-18T12:07:46.146Z</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>26</v>
+        <v>1265</v>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>3463363</t>
+          <t>3391461</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Jennifer Allen', 'phone': '2817331351', 'email': 'jenn@jenniferallenteam.com', 'website': 'http://www.jenniferallenteam.com'}</t>
+          <t>{'name': 'Cary Peach Reynolds', 'phone': '5129175000', 'email': 'peach@kaleidoproperties.com'}</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Exp Realty LLC', 'phone': '8885197431', 'email': 'djones@wandjlaw.com'}</t>
+          <t>{'name': 'Zilker Properties of Austin', 'phone': '5124401799', 'email': 'peach@zilkerproperties.com', 'website': 'zilkerproperties.com'}</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 125000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+          <t>{'2022-12-01': {'event': 'Sale Listing', 'price': 2250000, 'listingType': 'Standard', 'listedDate': '2022-12-01T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 1265}}</t>
         </is>
       </c>
       <c r="AF3" s="2" t="inlineStr"/>
@@ -902,23 +902,23 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11603-Vailrun-Dr,-Houston,-TX-77070</t>
+          <t>2004-Canonero-Dr,-Austin,-TX-78746</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>11603 Vailrun Dr, Houston, TX 77070</t>
+          <t>2004 Canonero Dr, Austin, TX 78746</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11603 Vailrun Dr</t>
+          <t>2004 Canonero Dr</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -933,24 +933,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77070</t>
+          <t>78746</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>29.975319</v>
+        <v>30.31965</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-95.597576</v>
+        <v>-97.813681</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>2556</v>
+        <v>5867</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>8969</v>
+        <v>55234</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1991</v>
+        <v>1998</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>347500</v>
+        <v>3250000</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
@@ -987,78 +987,78 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2024-03-06T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01T00:00:00.000Z</t>
+          <t>2022-12-02T08:47:00.574Z</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.491Z</t>
+          <t>2026-05-18T12:07:46.145Z</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>26</v>
+        <v>804</v>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>67844418</t>
+          <t>4807765</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Elizabeth Wallace', 'phone': '8325197982', 'email': 'lizwallacesold@gmail.com', 'website': 'http://lizwallacesold.com/'}</t>
+          <t>{'name': 'Brendan Doherty', 'phone': '5126327474', 'email': 'brendan@realtyaustin.com', 'website': 'http://www.realtyaustin.com/agents/brendan-doherty.php'}</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'RE MAX Associates Northeast', 'phone': '2813588888', 'email': 'maria.west1@remax.net', 'website': 'www.northhoustonhomes.com'}</t>
+          <t>{'name': 'Compass RE Texas', 'phone': '5122411300', 'email': 'realtor@realtyaustin.com', 'website': 'http://realtyaustin.com'}</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>{'2026-03-31': {'event': 'Sale Listing', 'price': 359000, 'listingType': 'Standard', 'listedDate': '2026-03-31T00:00:00.000Z', 'removedDate': '2026-04-16T00:00:00.000Z', 'daysOnMarket': 16}, '2026-04-23': {'event': 'Sale Listing', 'price': 347500, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+          <t>{'2024-03-06': {'event': 'Sale Listing', 'price': 3250000, 'listingType': 'Standard', 'listedDate': '2024-03-06T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 804}}</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 63}</t>
+          <t>{'fee': 57}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>8206-Colonial--B-Ln,-Unit-A,-Houston,-TX-77051</t>
+          <t>901-Valdez-St,-Unit-1-3,-Austin,-TX-78741</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>8206 Colonial /B Ln, Unit A, Houston, TX 77051</t>
+          <t>901 Valdez St, Unit 1-3, Austin, TX 78741</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8206 Colonial /B Ln</t>
+          <t>901 Valdez St</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Unit A</t>
+          <t>Unit 1-3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1073,24 +1073,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77051</t>
+          <t>78741</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>29.672921</v>
+        <v>30.233204</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-95.368985</v>
+        <v>-97.692787</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         <v>3</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>3396</v>
+        <v>1728</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>5000</v>
+        <v>7318</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>2026</v>
+        <v>1965</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>New Construction</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2024-02-03T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28T00:00:00.000Z</t>
+          <t>2021-02-11T13:53:10.141Z</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.490Z</t>
+          <t>2026-05-18T12:07:46.141Z</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>26</v>
+        <v>836</v>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>6194906</t>
+          <t>3565833</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Jamila Hodge', 'phone': '2812425829', 'email': 'jhodgerealestate@gmail.com', 'website': 'http://cbunited.com/jamila.hodge'}</t>
+          <t>{'name': 'Eunice Garza', 'phone': '5127865192', 'email': 'eunicegarza@gmail.com', 'website': 'http://www.facebook.com/dr-eunice-garza-resident-realty-1679274039005550'}</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Nextgen Real Estate Properties', 'phone': '2817637232', 'email': 'jennifer@houstonhomeblueprint.com'}</t>
+          <t>{'name': 'Properties Plus', 'phone': '5127865192', 'website': 'www.prop-plus.com'}</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 599000, 'listingType': 'New Construction', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+          <t>{'2024-02-03': {'event': 'Sale Listing', 'price': 599000, 'listingType': 'Standard', 'listedDate': '2024-02-03T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 836}}</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr"/>
@@ -1174,27 +1174,23 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>8601-Amadwe--B-St,-Unit-A,-Houston,-TX-77051</t>
+          <t>2314-Big-Horn-Dr,-Austin,-TX-78734</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8601 Amadwe /B St, Unit A, Houston, TX 77051</t>
+          <t>2314 Big Horn Dr, Austin, TX 78734</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8601 Amadwe /B St</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Unit A</t>
-        </is>
-      </c>
+          <t>2314 Big Horn Dr</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1209,124 +1205,120 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77051</t>
+          <t>78734</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>29.668211</v>
+        <v>30.373902</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-95.35651300000001</v>
+        <v>-97.91634999999999</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Multi-Family</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>3590</v>
-      </c>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="n">
-        <v>4400</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>2026</v>
-      </c>
+        <v>9278</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>545000</v>
+        <v>236000</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>New Construction</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2024-04-08T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24T00:00:00.000Z</t>
+          <t>2022-05-22T10:30:44.867Z</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.487Z</t>
+          <t>2026-05-18T12:07:46.141Z</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>26</v>
+        <v>771</v>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>25293742</t>
+          <t>1368718</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Moji Oladunjoye', 'phone': '8327798098'}</t>
+          <t>{'name': 'Adam Baker', 'phone': '5127208656', 'email': 'adam.baker@compass.com', 'website': 'http://www.adambakeratx.com'}</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Mo Maison Realty', 'phone': '8327798098', 'email': 'moji@mo-maison.com'}</t>
+          <t>{'name': 'Compass RE Texas', 'phone': '5122411300', 'email': 'realtor@realtyaustin.com', 'website': 'http://realtyaustin.com'}</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 545000, 'listingType': 'New Construction', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr"/>
+          <t>{'2024-04-08': {'event': 'Sale Listing', 'price': 236000, 'listingType': 'Standard', 'listedDate': '2024-04-08T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 771}}</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 9}</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>501-Detering-St,-Houston,-TX-77007</t>
+          <t>4901-Lambs-Ln,-Austin,-TX-78744</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>501 Detering St, Houston, TX 77007</t>
+          <t>4901 Lambs Ln, Austin, TX 78744</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>501 Detering St</t>
+          <t>4901 Lambs Ln</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1341,44 +1333,44 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>78744</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>29.76682</v>
+        <v>30.178172</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-95.416451</v>
+        <v>-97.752184</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>2372</v>
+        <v>1234</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>2136</v>
+        <v>10934</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>1999</v>
+        <v>1983</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1378,7 @@
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>484000</v>
+        <v>375000</v>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
@@ -1395,46 +1387,46 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2022-10-16T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24T00:00:00.000Z</t>
+          <t>2022-10-16T08:45:43.391Z</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.367Z</t>
+          <t>2026-05-18T12:07:46.140Z</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>26</v>
+        <v>1311</v>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>48776375</t>
+          <t>7768829</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Leah Oliver', 'phone': '8324442669', 'email': 'leah.oliver@sothebyshomes.com', 'website': 'https://www.sothebyshomes.com/houston'}</t>
+          <t>{'name': 'Neil Ally', 'phone': '5127910958', 'email': 'mally0824@yahoo.com'}</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Compass RE Texas LLC - Westheimer', 'phone': '8328994788', 'email': 'txbroker@compass.com', 'website': 'http://www.compass.com'}</t>
+          <t>{'name': 'Water Lily Realty', 'phone': '5122996402', 'email': 'mally.pi@att.net'}</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 484000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+          <t>{'2022-10-16': {'event': 'Sale Listing', 'price': 375000, 'listingType': 'Standard', 'listedDate': '2022-10-16T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 1311}}</t>
         </is>
       </c>
       <c r="AF7" s="2" t="inlineStr"/>
@@ -1442,23 +1434,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2236-Ann-St,-Houston,-TX-77003</t>
+          <t>44-East-Ave,-Unit-1802,-Austin,-TX-78701</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2236 Ann St, Houston, TX 77003</t>
+          <t>44 East Ave, Unit 1802, Austin, TX 78701</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2236 Ann St</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>44 East Ave</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1802</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1473,44 +1469,42 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77003</t>
+          <t>78701</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>29.760342</v>
+        <v>30.255883</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-95.34624599999999</v>
+        <v>-97.73894</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1656</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>1400</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="n">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
@@ -1518,7 +1512,7 @@
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>310000</v>
+        <v>569000</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
@@ -1527,70 +1521,74 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2023-08-23T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2025-05-21T00:00:00.000Z</t>
+          <t>2023-08-24T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.363Z</t>
+          <t>2026-05-18T12:07:46.138Z</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>8232513</t>
+          <t>2228207</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Marcus Ruiz', 'phone': '3462341001', 'email': 'marcruiz04@gmail.com'}</t>
+          <t>{'name': 'Azucena Daguer', 'phone': '5122994489', 'email': 'agentdaguer@gmail.com'}</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Re/Max Signature', 'phone': '7139005003', 'email': 'roxie@remaxsignaturetx.com'}</t>
+          <t>{'name': 'Ultima Real Estate Services', 'phone': '5123728237', 'email': 'ultimaceo@gmail.com', 'website': 'http://www.ultimarealestate.com'}</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>{'2025-05-20': {'event': 'Sale Listing', 'price': 310000, 'listingType': 'Standard', 'listedDate': '2025-05-20T00:00:00.000Z', 'removedDate': '2025-05-22T00:00:00.000Z', 'daysOnMarket': 2}, '2026-04-23': {'event': 'Sale Listing', 'price': 310000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="inlineStr"/>
+          <t>{'2023-08-23': {'event': 'Sale Listing', 'price': 569000, 'listingType': 'Standard', 'listedDate': '2023-08-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 1000}}</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>{'fee': 381}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1427-Basswood-Springs-Ct,-Houston,-TX-77062</t>
+          <t>1806-Fortview-Rd,-Austin,-TX-78704</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1427 Basswood Springs Ct, Houston, TX 77062</t>
+          <t>1806 Fortview Rd, Austin, TX 78704</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1427 Basswood Springs Ct</t>
+          <t>1806 Fortview Rd</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1605,44 +1603,44 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77062</t>
+          <t>78704</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>29.585769</v>
+        <v>30.230799</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-95.151549</v>
+        <v>-97.786053</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Land</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2227</v>
+        <v>1380</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>11147</v>
+        <v>28750</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>1993</v>
+        <v>1948</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
@@ -1650,7 +1648,7 @@
         </is>
       </c>
       <c r="T9" s="2" t="n">
-        <v>410000</v>
+        <v>999999</v>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
@@ -1659,74 +1657,70 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2023-07-11T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28T00:00:00.000Z</t>
+          <t>2023-07-12T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.362Z</t>
+          <t>2026-05-18T12:07:46.136Z</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>26</v>
+        <v>1043</v>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>70583215</t>
+          <t>6159568</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Michael Nassif', 'email': 'michael.nassif@nrerealty.com', 'website': 'http://nrerealty.com'}</t>
+          <t>{'name': 'Christopher Watters, Realtor | Broker', 'phone': '7373135275', 'email': 'sold@wattersinternational.com', 'website': 'http://www.christopherwatters.com'}</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Nre Realty', 'phone': '2813007189', 'email': 'michael.nassif@nrerealty.com', 'website': 'http://nrerealty.com'}</t>
+          <t>{'name': 'Watters International Realty', 'phone': '5126460038', 'email': 'chriswatters@wattersinternational.com', 'website': 'www.christopherwatters.com'}</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>{'2026-02-27': {'event': 'Sale Listing', 'price': 430000, 'listingType': 'Standard', 'listedDate': '2026-02-27T00:00:00.000Z', 'removedDate': '2026-03-26T00:00:00.000Z', 'daysOnMarket': 27}, '2026-04-23': {'event': 'Sale Listing', 'price': 410000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
-        </is>
-      </c>
-      <c r="AF9" s="2" t="inlineStr">
-        <is>
-          <t>{'fee': 71}</t>
-        </is>
-      </c>
+          <t>{'2023-07-11': {'event': 'Sale Listing', 'price': 999999, 'listingType': 'Standard', 'listedDate': '2023-07-11T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 1043}}</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>8903-Railton-St,-Houston,-TX-77080</t>
+          <t>1509-Parkway,-Austin,-TX-78703</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>8903 Railton St, Houston, TX 77080</t>
+          <t>1509 Parkway, Austin, TX 78703</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8903 Railton St</t>
+          <t>1509 Parkway</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1741,28 +1735,28 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77080</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>29.828289</v>
+        <v>30.279754</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-95.511835</v>
+        <v>-97.751265</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Multi-Family</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
@@ -1772,13 +1766,13 @@
         <v>2</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2174</v>
+        <v>2256</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>9361</v>
+        <v>8089</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>1960</v>
+        <v>1965</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
@@ -1786,7 +1780,7 @@
         </is>
       </c>
       <c r="T10" s="2" t="n">
-        <v>425000</v>
+        <v>1200000</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
@@ -1795,46 +1789,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2023-02-21T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2023-09-29T00:00:00.000Z</t>
+          <t>2023-02-22T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.361Z</t>
+          <t>2026-05-18T12:07:46.129Z</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>26</v>
+        <v>1183</v>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>46758823</t>
+          <t>6953086</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Jordana Ford', 'phone': '2817886241', 'email': 'info@jordanaford.com', 'website': 'http://www.homeinwesthouston.com'}</t>
+          <t>{'name': 'Samuel Pritchard', 'phone': '5123321864', 'email': 'pritchard@hpaoffice.com', 'website': 'http://www.harrisonpearson.com/'}</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Compass RE Texas LLC - The Heights', 'phone': '2817299246', 'email': 'txbroker@compass.com', 'website': 'http://www.compass.com'}</t>
+          <t>{'name': 'Harrison-Pearson Assoc.', 'phone': '5124726201', 'email': 'herb@hpaoffice.com', 'website': 'www.harrisonpearson.com'}</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>{'2025-10-23': {'event': 'Sale Listing', 'price': 460000, 'listingType': 'Standard', 'listedDate': '2025-10-23T00:00:00.000Z', 'removedDate': '2026-01-07T00:00:00.000Z', 'daysOnMarket': 76}, '2026-01-07': {'event': 'Sale Listing', 'price': 438000, 'listingType': 'Standard', 'listedDate': '2026-01-07T00:00:00.000Z', 'removedDate': '2026-04-23T00:00:00.000Z', 'daysOnMarket': 106}, '2026-04-23': {'event': 'Sale Listing', 'price': 425000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+          <t>{'2023-02-21': {'event': 'Sale Listing', 'price': 1200000, 'listingType': 'Standard', 'listedDate': '2023-02-21T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 1183}}</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -1842,23 +1836,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>18010-Quiet-Stream-Ct,-Houston,-TX-77095</t>
+          <t>48-East-Ave,-Unit-1305,-Austin,-TX-78701</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>18010 Quiet Stream Ct, Houston, TX 77095</t>
+          <t>48 East Ave, Unit 1305, Austin, TX 78701</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18010 Quiet Stream Ct</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>48 East Ave</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1305</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1873,44 +1871,44 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77095</t>
+          <t>78701</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>29.889556</v>
+        <v>30.256396</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-95.682858</v>
+        <v>-97.738839</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>2461</v>
+        <v>706</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>8075</v>
+        <v>61</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>1994</v>
+        <v>2021</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
@@ -1918,7 +1916,7 @@
         </is>
       </c>
       <c r="T11" s="2" t="n">
-        <v>349000</v>
+        <v>660000</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
@@ -1927,51 +1925,51 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23T00:00:00.000Z</t>
+          <t>2023-11-01T00:00:00.000Z</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24T00:00:00.000Z</t>
+          <t>2023-05-11T00:00:00.000Z</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T12:10:29.360Z</t>
+          <t>2026-05-18T12:07:46.128Z</t>
         </is>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>26</v>
+        <v>930</v>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>UnlockMLS</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>56512593</t>
+          <t>1464045</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Tina Vu', 'phone': '8327329772'}</t>
+          <t>{'name': 'Eric Harper', 'phone': '5127693530', 'email': 'eric@allstreetsrealty.com'}</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>{'name': 'Walzel Properties', 'phone': '7135044874', 'email': 'shellywazel@gmail.com', 'website': 'http://www.walzelproperties.com'}</t>
+          <t>{'name': 'All Streets Realty, Llc', 'phone': '5129645975', 'email': 'craig@allstreetsrealty.com'}</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>{'2026-04-23': {'event': 'Sale Listing', 'price': 349000, 'listingType': 'Standard', 'listedDate': '2026-04-23T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 26}}</t>
+          <t>{'2023-11-01': {'event': 'Sale Listing', 'price': 660000, 'listingType': 'Standard', 'listedDate': '2023-11-01T00:00:00.000Z', 'removedDate': None, 'daysOnMarket': 930}}</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>{'fee': 73}</t>
+          <t>{'fee': 467}</t>
         </is>
       </c>
     </row>
